--- a/발주서-웹서비스/backend/templates/테무_배송확인_템플릿.xlsx
+++ b/발주서-웹서비스/backend/templates/테무_배송확인_템플릿.xlsx
@@ -20,7 +20,7 @@
     <t>주문 ID</t>
   </si>
   <si>
-    <t>주문 상품 id</t>
+    <t>상품 주문 ID</t>
   </si>
   <si>
     <t>수량</t>
